--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_96_R10.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_96_R10.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.0904</v>
+        <v>4.8943</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0525</v>
+        <v>5.4195</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.9621</v>
+        <v>-0.5252</v>
       </c>
       <c r="G2" t="n">
         <v>0.2132</v>
@@ -610,13 +610,13 @@
         <v>1.8556</v>
       </c>
       <c r="S2" t="n">
-        <v>1.3412</v>
+        <v>1.145</v>
       </c>
       <c r="T2" t="n">
-        <v>1.8442</v>
+        <v>1.2111</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.503</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="V2" t="n">
         <v>2.1444</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>K. KAMENJAS</t>
+          <t>K. PREPELIC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.0516</v>
+        <v>4.642</v>
       </c>
       <c r="E3" t="n">
-        <v>5.0082</v>
+        <v>5.1905</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.9565</v>
+        <v>-0.5486</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8519</v>
+        <v>3.1997</v>
       </c>
       <c r="H3" t="n">
-        <v>2.7991</v>
+        <v>0.8609</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.9473</v>
+        <v>2.3388</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4858</v>
+        <v>4.0041</v>
       </c>
       <c r="K3" t="n">
-        <v>2.7497</v>
+        <v>1.294</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7361</v>
+        <v>2.7101</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.6339</v>
+        <v>-0.8044</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0495</v>
+        <v>-0.4331</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.6834</v>
+        <v>-0.3713</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4639</v>
+        <v>0.9278</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.3917</v>
+        <v>-0.4639</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8556</v>
+        <v>1.3917</v>
       </c>
       <c r="S3" t="n">
-        <v>3.5245</v>
+        <v>1.0506</v>
       </c>
       <c r="T3" t="n">
-        <v>2.6305</v>
+        <v>0.5780999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>0.894</v>
+        <v>0.4725</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.7886</v>
+        <v>-0.5361</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2836</v>
+        <v>1.0722</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0722</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>K. PREPELIC</t>
+          <t>A. AVRAMOVIC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,40 +721,40 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.7245</v>
+        <v>4.5197</v>
       </c>
       <c r="E4" t="n">
-        <v>4.1722</v>
+        <v>6.3375</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4477</v>
+        <v>-1.8178</v>
       </c>
       <c r="G4" t="n">
-        <v>3.1997</v>
+        <v>0.6151</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8609</v>
+        <v>-0.6697</v>
       </c>
       <c r="I4" t="n">
-        <v>2.3388</v>
+        <v>1.2848</v>
       </c>
       <c r="J4" t="n">
-        <v>4.0041</v>
+        <v>2.1664</v>
       </c>
       <c r="K4" t="n">
-        <v>1.294</v>
+        <v>-0.383</v>
       </c>
       <c r="L4" t="n">
-        <v>2.7101</v>
+        <v>2.5495</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.8044</v>
+        <v>-1.5513</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4331</v>
+        <v>-0.2866</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3713</v>
+        <v>-1.2647</v>
       </c>
       <c r="P4" t="n">
         <v>0.9278</v>
@@ -766,28 +766,28 @@
         <v>1.3917</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1331</v>
+        <v>-0.2399</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4402</v>
+        <v>0.3462</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5733</v>
+        <v>-0.586</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.5361</v>
+        <v>3.2166</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0722</v>
+        <v>4.2888</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.6083</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. AVRAMOVIC</t>
+          <t>K. KAMENJAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.6358</v>
+        <v>2.0456</v>
       </c>
       <c r="E5" t="n">
-        <v>5.3192</v>
+        <v>3.5062</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.6834</v>
+        <v>-1.4606</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6151</v>
+        <v>0.8519</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6697</v>
+        <v>2.7991</v>
       </c>
       <c r="I5" t="n">
-        <v>1.2848</v>
+        <v>-1.9473</v>
       </c>
       <c r="J5" t="n">
-        <v>2.1664</v>
+        <v>3.4858</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.383</v>
+        <v>2.7497</v>
       </c>
       <c r="L5" t="n">
-        <v>2.5495</v>
+        <v>0.7361</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.5513</v>
+        <v>-2.6339</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2866</v>
+        <v>0.0495</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.2647</v>
+        <v>-2.6834</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.4639</v>
+        <v>-1.3917</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3917</v>
+        <v>1.8556</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.1237</v>
+        <v>1.5184</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6721</v>
+        <v>1.1286</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4516</v>
+        <v>0.3899</v>
       </c>
       <c r="V5" t="n">
-        <v>3.2166</v>
+        <v>-0.7886</v>
       </c>
       <c r="W5" t="n">
-        <v>4.2888</v>
+        <v>0.2836</v>
       </c>
       <c r="X5" t="n">
         <v>-1.0722</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F. PETRUSEV</t>
+          <t>B. ELLIS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2932</v>
+        <v>0.311</v>
       </c>
       <c r="E6" t="n">
-        <v>2.2522</v>
+        <v>0.8849</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.959</v>
+        <v>-0.5738</v>
       </c>
       <c r="G6" t="n">
-        <v>1.1425</v>
+        <v>0.5198</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1319</v>
+        <v>0.1417</v>
       </c>
       <c r="I6" t="n">
-        <v>1.0106</v>
+        <v>0.3781</v>
       </c>
       <c r="J6" t="n">
-        <v>2.9904</v>
+        <v>0.6057</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4509</v>
+        <v>0.0168</v>
       </c>
       <c r="L6" t="n">
-        <v>2.5395</v>
+        <v>0.5889</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.848</v>
+        <v>-0.0859</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.319</v>
+        <v>0.1249</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.529</v>
+        <v>-0.2108</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.4639</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.8556</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8556</v>
+        <v>0.4639</v>
       </c>
       <c r="S6" t="n">
-        <v>1.5477</v>
+        <v>-0.1366</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8338</v>
+        <v>0.2792</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7139</v>
+        <v>-0.4158</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.3969</v>
+        <v>-0.5361</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2836</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.6805</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. ABASS</t>
+          <t>D. BERTANS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1613</v>
+        <v>0.2177</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3881</v>
+        <v>0.0832</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5494</v>
+        <v>0.1345</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.0292</v>
+        <v>-0.4389</v>
       </c>
       <c r="H7" t="n">
-        <v>0.52</v>
+        <v>0.8729</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.5492</v>
+        <v>-1.3118</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.7501</v>
+        <v>-0.3062</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6385999999999999</v>
+        <v>1.1595</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.3887</v>
+        <v>-1.4658</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2791</v>
+        <v>-0.1326</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1186</v>
+        <v>-0.2866</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1605</v>
+        <v>0.154</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.4639</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2627</v>
+        <v>0.1926</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8259</v>
+        <v>0.8532999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5632</v>
+        <v>-0.6607</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B. ELLIS</t>
+          <t>D. BACON</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1511</v>
+        <v>0.06469999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4563</v>
+        <v>0.3183</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6075</v>
+        <v>-0.2536</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5198</v>
+        <v>0.106</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1417</v>
+        <v>0.4908</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3781</v>
+        <v>-0.3849</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6057</v>
+        <v>2.1826</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0168</v>
+        <v>0.9347</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5889</v>
+        <v>1.2479</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0859</v>
+        <v>-2.0766</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1249</v>
+        <v>-0.4439</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2108</v>
+        <v>-1.6327</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4639</v>
+        <v>-2.5515</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-3.7112</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4639</v>
+        <v>1.1598</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5988</v>
+        <v>0.7912</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1494</v>
+        <v>0.7747000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4494</v>
+        <v>0.0165</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.5361</v>
+        <v>1.719</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5361</v>
+        <v>0.6468</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. BACON</t>
+          <t>A. ABASS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4572</v>
+        <v>-0.0267</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0356</v>
+        <v>-0.7105</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4216</v>
+        <v>0.6838</v>
       </c>
       <c r="G9" t="n">
-        <v>0.106</v>
+        <v>-1.0292</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4908</v>
+        <v>0.52</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3849</v>
+        <v>-1.5492</v>
       </c>
       <c r="J9" t="n">
-        <v>2.1826</v>
+        <v>-0.7501</v>
       </c>
       <c r="K9" t="n">
-        <v>0.9347</v>
+        <v>0.6385999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>1.2479</v>
+        <v>-1.3887</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.0766</v>
+        <v>-0.2791</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4439</v>
+        <v>-0.1186</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.6327</v>
+        <v>-0.1605</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.5515</v>
+        <v>0.9278</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.7112</v>
+        <v>-0.4639</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1598</v>
+        <v>1.3917</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2693</v>
+        <v>0.0747</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4208</v>
+        <v>0.5034</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1516</v>
+        <v>-0.4288</v>
       </c>
       <c r="V9" t="n">
-        <v>1.719</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.6468</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. BERTANS</t>
+          <t>F. PETRUSEV</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.7156</v>
+        <v>-0.0525</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5813</v>
+        <v>2.2089</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1344</v>
+        <v>-2.2614</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.4389</v>
+        <v>1.1425</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8729</v>
+        <v>0.1319</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.3118</v>
+        <v>1.0106</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3062</v>
+        <v>2.9904</v>
       </c>
       <c r="K10" t="n">
-        <v>1.1595</v>
+        <v>0.4509</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.4658</v>
+        <v>2.5395</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.1326</v>
+        <v>-1.848</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2866</v>
+        <v>-0.319</v>
       </c>
       <c r="O10" t="n">
-        <v>0.154</v>
+        <v>-1.529</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4639</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.4639</v>
+        <v>-1.8556</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9278</v>
+        <v>1.8556</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7407</v>
+        <v>1.2019</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1889</v>
+        <v>0.7905</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.9296</v>
+        <v>0.4114</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-2.3969</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.2836</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-2.6805</v>
       </c>
     </row>
     <row r="11">
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.5999</v>
+        <v>-1.8358</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.1808</v>
+        <v>-1.4167</v>
       </c>
       <c r="F11" t="n">
         <v>-0.4191</v>
@@ -1312,10 +1312,10 @@
         <v>0.4639</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3971</v>
+        <v>0.1612</v>
       </c>
       <c r="T11" t="n">
-        <v>0.7117</v>
+        <v>0.4758</v>
       </c>
       <c r="U11" t="n">
         <v>-0.3145</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>14.033</v>
+        <v>14.78</v>
       </c>
       <c r="E12" t="n">
-        <v>21.0748</v>
+        <v>21.8218</v>
       </c>
       <c r="F12" t="n">
-        <v>-7.041900000000001</v>
+        <v>-7.0418</v>
       </c>
       <c r="G12" t="n">
         <v>4.415</v>
@@ -1360,7 +1360,7 @@
         <v>6.506200000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.0915</v>
+        <v>-2.091499999999999</v>
       </c>
       <c r="J12" t="n">
         <v>16.032</v>
@@ -1369,7 +1369,7 @@
         <v>8.370799999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>7.6612</v>
+        <v>7.661200000000002</v>
       </c>
       <c r="M12" t="n">
         <v>-11.617</v>
@@ -1390,16 +1390,16 @@
         <v>12.7573</v>
       </c>
       <c r="S12" t="n">
-        <v>5.0124</v>
+        <v>5.7591</v>
       </c>
       <c r="T12" t="n">
-        <v>6.194100000000001</v>
+        <v>6.940899999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.1817</v>
+        <v>-1.1816</v>
       </c>
       <c r="V12" t="n">
-        <v>2.286200000000001</v>
+        <v>2.2862</v>
       </c>
       <c r="W12" t="n">
         <v>9.2866</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.1111</v>
+        <v>2.898</v>
       </c>
       <c r="E13" t="n">
-        <v>7.0153</v>
+        <v>5.8358</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.9041</v>
+        <v>-2.9377</v>
       </c>
       <c r="G13" t="n">
         <v>0.097</v>
@@ -1468,13 +1468,13 @@
         <v>1.3917</v>
       </c>
       <c r="S13" t="n">
-        <v>1.5503</v>
+        <v>0.3372</v>
       </c>
       <c r="T13" t="n">
-        <v>2.2255</v>
+        <v>1.046</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6752</v>
+        <v>-0.7088</v>
       </c>
       <c r="V13" t="n">
         <v>1.0722</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. DAVIDOVAC</t>
+          <t>O. DOBRIC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,40 +1501,40 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.511</v>
+        <v>1.7269</v>
       </c>
       <c r="E14" t="n">
-        <v>2.6905</v>
+        <v>2.846</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.1795</v>
+        <v>-1.1191</v>
       </c>
       <c r="G14" t="n">
-        <v>0.081</v>
+        <v>1.4183</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0374</v>
+        <v>-0.0406</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0436</v>
+        <v>1.4589</v>
       </c>
       <c r="J14" t="n">
-        <v>1.5501</v>
+        <v>2.9086</v>
       </c>
       <c r="K14" t="n">
-        <v>0.9747</v>
+        <v>0.2353</v>
       </c>
       <c r="L14" t="n">
-        <v>0.5754</v>
+        <v>2.6733</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.4691</v>
+        <v>-1.4903</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.9373</v>
+        <v>-0.2759</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.5319</v>
+        <v>-1.2144</v>
       </c>
       <c r="P14" t="n">
         <v>1.3917</v>
@@ -1546,28 +1546,28 @@
         <v>1.3917</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1801</v>
+        <v>-1.0831</v>
       </c>
       <c r="T14" t="n">
-        <v>1.1404</v>
+        <v>-0.0626</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.9603</v>
+        <v>-1.0205</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>O. DOBRIC</t>
+          <t>D. DAVIDOVAC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,40 +1579,40 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9685</v>
+        <v>1.2916</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0203</v>
+        <v>2.3367</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.0519</v>
+        <v>-1.0451</v>
       </c>
       <c r="G15" t="n">
-        <v>1.4183</v>
+        <v>0.081</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.0406</v>
+        <v>0.0374</v>
       </c>
       <c r="I15" t="n">
-        <v>1.4589</v>
+        <v>0.0436</v>
       </c>
       <c r="J15" t="n">
-        <v>2.9086</v>
+        <v>1.5501</v>
       </c>
       <c r="K15" t="n">
-        <v>0.2353</v>
+        <v>0.9747</v>
       </c>
       <c r="L15" t="n">
-        <v>2.6733</v>
+        <v>0.5754</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.4903</v>
+        <v>-1.4691</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2759</v>
+        <v>-0.9373</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.2144</v>
+        <v>-0.5319</v>
       </c>
       <c r="P15" t="n">
         <v>1.3917</v>
@@ -1624,22 +1624,22 @@
         <v>1.3917</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.8415</v>
+        <v>-0.0393</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8883</v>
+        <v>0.7866</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.9533</v>
+        <v>-0.8259</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3102</v>
+        <v>-0.2745</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8984</v>
+        <v>0.9548</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.5882</v>
+        <v>-1.2293</v>
       </c>
       <c r="G16" t="n">
         <v>-0.717</v>
@@ -1702,13 +1702,13 @@
         <v>1.3917</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4885</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>1.4787</v>
+        <v>0.5351</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.9902</v>
+        <v>-0.6313</v>
       </c>
       <c r="V16" t="n">
         <v>1.4665</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.8264</v>
+        <v>-0.8702</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9247</v>
+        <v>1.1606</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.7511</v>
+        <v>-2.0307</v>
       </c>
       <c r="G17" t="n">
         <v>1.8446</v>
@@ -1780,13 +1780,13 @@
         <v>0.232</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0242</v>
+        <v>-0.0679</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6721</v>
+        <v>-0.4362</v>
       </c>
       <c r="U17" t="n">
-        <v>0.648</v>
+        <v>0.3684</v>
       </c>
       <c r="V17" t="n">
         <v>-1.719</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.5022</v>
+        <v>-1.0076</v>
       </c>
       <c r="E18" t="n">
-        <v>1.1524</v>
+        <v>1.6242</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.6547</v>
+        <v>-2.6318</v>
       </c>
       <c r="G18" t="n">
         <v>1.4487</v>
@@ -1858,13 +1858,13 @@
         <v>1.6237</v>
       </c>
       <c r="S18" t="n">
-        <v>-2.2009</v>
+        <v>-1.7062</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.0455</v>
+        <v>-0.5737</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.1554</v>
+        <v>-1.1325</v>
       </c>
       <c r="V18" t="n">
         <v>-1.214</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.4267</v>
+        <v>-2.0392</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1686</v>
+        <v>0.5225</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.5953</v>
+        <v>-2.5617</v>
       </c>
       <c r="G19" t="n">
         <v>1.636</v>
@@ -1936,13 +1936,13 @@
         <v>0.232</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3668</v>
+        <v>0.0206</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5228</v>
+        <v>-0.1689</v>
       </c>
       <c r="U19" t="n">
-        <v>0.156</v>
+        <v>0.1896</v>
       </c>
       <c r="V19" t="n">
         <v>-1.6083</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.4812</v>
+        <v>-2.2903</v>
       </c>
       <c r="E20" t="n">
         <v>-1.1272</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.3539</v>
+        <v>-1.1631</v>
       </c>
       <c r="G20" t="n">
         <v>-0.9546</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3668</v>
+        <v>-0.1759</v>
       </c>
       <c r="T20" t="n">
         <v>-0.0747</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2921</v>
+        <v>-0.1013</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.0613</v>
+        <v>-3.2801</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.7824</v>
+        <v>-2.9004</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.2788</v>
+        <v>-0.3797</v>
       </c>
       <c r="G22" t="n">
         <v>-2.2854</v>
@@ -2170,13 +2170,13 @@
         <v>1.1598</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4714</v>
+        <v>0.2526</v>
       </c>
       <c r="T22" t="n">
-        <v>0.8768</v>
+        <v>0.7589</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4055</v>
+        <v>-0.5063</v>
       </c>
       <c r="V22" t="n">
         <v>1.0722</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.8839</v>
+        <v>-6.6493</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.8234</v>
+        <v>-2.1157</v>
       </c>
       <c r="F23" t="n">
-        <v>-5.0605</v>
+        <v>-4.5336</v>
       </c>
       <c r="G23" t="n">
         <v>-6.1437</v>
@@ -2248,13 +2248,13 @@
         <v>1.3917</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.5958</v>
+        <v>-1.3612</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.187</v>
+        <v>-0.4793</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.4088</v>
+        <v>-0.8819</v>
       </c>
       <c r="V23" t="n">
         <v>-0.5361</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-14.0331</v>
+        <v>-13.2469</v>
       </c>
       <c r="E24" t="n">
-        <v>7.041700000000002</v>
+        <v>7.041799999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>-21.0747</v>
+        <v>-20.2885</v>
       </c>
       <c r="G24" t="n">
         <v>-4.415</v>
@@ -2296,13 +2296,13 @@
         <v>-6.506399999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>2.091599999999999</v>
+        <v>2.0916</v>
       </c>
       <c r="J24" t="n">
         <v>11.6171</v>
       </c>
       <c r="K24" t="n">
-        <v>1.8645</v>
+        <v>1.864500000000001</v>
       </c>
       <c r="L24" t="n">
         <v>9.752600000000001</v>
@@ -2326,13 +2326,13 @@
         <v>10.438</v>
       </c>
       <c r="S24" t="n">
-        <v>-5.0123</v>
+        <v>-4.226</v>
       </c>
       <c r="T24" t="n">
-        <v>1.1816</v>
+        <v>1.1818</v>
       </c>
       <c r="U24" t="n">
-        <v>-6.194100000000001</v>
+        <v>-5.4078</v>
       </c>
       <c r="V24" t="n">
         <v>-2.286199999999999</v>
